--- a/erp_exchange/samples/missing_columns.xlsx
+++ b/erp_exchange/samples/missing_columns.xlsx
@@ -436,16 +436,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DXTR1000</t>
+          <t>BOOK1001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1200</v>
+        <v>9.99</v>
       </c>
     </row>
   </sheetData>

--- a/erp_exchange/samples/missing_columns.xlsx
+++ b/erp_exchange/samples/missing_columns.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BOOK1001</t>
+          <t>9780451524935</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
